--- a/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631796596</v>
+        <v>10.84497617501228</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907189225882</v>
+        <v>37.78907139414</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.335397861953915</v>
+        <v>7.050912011900593</v>
       </c>
       <c r="C2" t="n">
-        <v>10.55575131606171</v>
+        <v>5.222897786593031</v>
       </c>
       <c r="D2" t="n">
-        <v>23.09561474240622</v>
+        <v>30.02871702979719</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.65534980254714</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="C3" t="n">
-        <v>34.46425315758428</v>
+        <v>20.82777754559608</v>
       </c>
       <c r="D3" t="n">
-        <v>76.02163347835176</v>
+        <v>101.2083708308037</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>41.33845058272045</v>
       </c>
       <c r="C4" t="n">
-        <v>64.38792318302706</v>
+        <v>56.00281604105505</v>
       </c>
       <c r="D4" t="n">
-        <v>105.3562548812465</v>
+        <v>115.8089226883622</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.53421928649306</v>
+        <v>52.05717201768713</v>
       </c>
       <c r="C5" t="n">
-        <v>108.2131407006047</v>
+        <v>96.55488671267382</v>
       </c>
       <c r="D5" t="n">
-        <v>78.83434065101889</v>
+        <v>80.84692344472485</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>47.81896717845365</v>
       </c>
       <c r="C6" t="n">
-        <v>130.3348617203981</v>
+        <v>100.9914045881652</v>
       </c>
       <c r="D6" t="n">
-        <v>50.95859633663495</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>121.5698182168825</v>
+        <v>81.14635649452011</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
         <v>33.9468721174462</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669929532092024</v>
+        <v>7.682669344414701</v>
       </c>
       <c r="C21" t="n">
-        <v>92.99789557661578</v>
+        <v>93.15236580102825</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669929532092024</v>
+        <v>8.643003012466538</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.742823159216341</v>
+        <v>8.920159640786519</v>
       </c>
       <c r="C2" t="n">
-        <v>11.31955102996572</v>
+        <v>8.805295159389642</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26112919379642</v>
+        <v>37.75212621910685</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4821612959722</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="C3" t="n">
-        <v>37.56166716448296</v>
+        <v>20.43998720241859</v>
       </c>
       <c r="D3" t="n">
-        <v>76.27688788145593</v>
+        <v>101.0611086751667</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.68081848959532</v>
+        <v>39.70482240285375</v>
       </c>
       <c r="C4" t="n">
-        <v>74.90440459091889</v>
+        <v>53.94801809606648</v>
       </c>
       <c r="D4" t="n">
-        <v>117.2128219054352</v>
+        <v>136.3313766979376</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.17297718905925</v>
+        <v>56.42594930158544</v>
       </c>
       <c r="C5" t="n">
-        <v>111.9437819767426</v>
+        <v>98.73927535462298</v>
       </c>
       <c r="D5" t="n">
-        <v>94.68956607460487</v>
+        <v>99.40195505498957</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.16864928761476</v>
+        <v>58.12339108222817</v>
       </c>
       <c r="C6" t="n">
-        <v>148.6091134872482</v>
+        <v>125.8669279183708</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26931163726245</v>
+        <v>63.03409309887072</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>44.85507085933252</v>
       </c>
       <c r="C7" t="n">
-        <v>153.369608105141</v>
+        <v>110.7902284242525</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.3600647277471</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>116.2438369213436</v>
+        <v>79.10923000820797</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>12.31406145436774</v>
       </c>
       <c r="C9" t="n">
-        <v>68.67030666895162</v>
+        <v>49.92187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14366362665208</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846030391717688</v>
+        <v>7.862905631771452</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0176412933652</v>
+        <v>101.2349100090574</v>
       </c>
       <c r="D21" t="n">
-        <v>8.8267841906824</v>
+        <v>9.828632039714314</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.274349577841365</v>
+        <v>9.56025914395544</v>
       </c>
       <c r="C2" t="n">
-        <v>8.734609324683872</v>
+        <v>5.168901662859456</v>
       </c>
       <c r="D2" t="n">
-        <v>22.75593003673682</v>
+        <v>29.9786478968806</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32508166329271</v>
+        <v>25.0247489812512</v>
       </c>
       <c r="C3" t="n">
-        <v>40.20747722742812</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D3" t="n">
-        <v>75.5945732270044</v>
+        <v>106.6227094197248</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.05169813762236</v>
+        <v>39.57719520130167</v>
       </c>
       <c r="C4" t="n">
-        <v>83.17464725149402</v>
+        <v>52.46754255806228</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1940298303343</v>
+        <v>149.0813341329909</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.17926858591223</v>
+        <v>57.43224069843842</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7858027118169</v>
+        <v>97.83115872819468</v>
       </c>
       <c r="D5" t="n">
-        <v>110.6184225760094</v>
+        <v>118.8651032916826</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.17243740971151</v>
+        <v>66.21397391292614</v>
       </c>
       <c r="C6" t="n">
-        <v>159.9198287878757</v>
+        <v>139.5927425714455</v>
       </c>
       <c r="D6" t="n">
-        <v>73.33851700264525</v>
+        <v>76.5989011284489</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.63926629084747</v>
+        <v>54.91602133245383</v>
       </c>
       <c r="C7" t="n">
-        <v>180.4982424165931</v>
+        <v>140.3742137440259</v>
       </c>
       <c r="D7" t="n">
-        <v>50.36463897556562</v>
+        <v>50.66407202536089</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.11939767148639</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="C8" t="n">
-        <v>152.2936126212865</v>
+        <v>107.7320843255237</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>17.9718734739421</v>
       </c>
       <c r="C9" t="n">
-        <v>99.84374152190058</v>
+        <v>70.9999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>57.51078051477815</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.006339554139183</v>
+        <v>8.027494862456749</v>
       </c>
       <c r="C21" t="n">
-        <v>109.0863764251464</v>
+        <v>109.3746175009732</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00792444267398</v>
+        <v>11.03780543587803</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.704935909378215</v>
+        <v>8.72577359534565</v>
       </c>
       <c r="C2" t="n">
-        <v>6.009277697694727</v>
+        <v>3.514656781203581</v>
       </c>
       <c r="D2" t="n">
-        <v>18.930059233287</v>
+        <v>24.80091050468292</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.8362123643068</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="C3" t="n">
-        <v>56.6959299202533</v>
+        <v>36.95789232637118</v>
       </c>
       <c r="D3" t="n">
-        <v>83.61545197070085</v>
+        <v>115.875681532251</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.13881164139307</v>
+        <v>27.59300097556086</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3006961727319</v>
+        <v>78.04403374910019</v>
       </c>
       <c r="D4" t="n">
-        <v>120.8246717093592</v>
+        <v>140.032565542948</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.94330497952772</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>95.54859531582083</v>
+        <v>83.39946747576656</v>
       </c>
       <c r="D5" t="n">
-        <v>73.55744674069228</v>
+        <v>77.70533079113505</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.44533790929634</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>118.8631397962741</v>
+        <v>92.45805354285189</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>107.0772586067911</v>
+        <v>75.75656159820512</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>52.32224389783376</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>43.82030877905637</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1971,7 +1971,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.496985322527138</v>
+        <v>5.282784396552087</v>
       </c>
       <c r="C2" t="n">
-        <v>3.529382996767283</v>
+        <v>2.305143609571511</v>
       </c>
       <c r="D2" t="n">
-        <v>13.34096955300991</v>
+        <v>16.93612964596172</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.27799883121787</v>
+        <v>30.59125846433061</v>
       </c>
       <c r="C3" t="n">
-        <v>40.56090640095697</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="D3" t="n">
-        <v>81.10217784782901</v>
+        <v>110.3042633106504</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.72437524148068</v>
+        <v>39.43680527959437</v>
       </c>
       <c r="C4" t="n">
-        <v>127.1039300257218</v>
+        <v>87.89685370892118</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2090180878052</v>
+        <v>163.2224280649619</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.52668410002858</v>
+        <v>40.91433557448583</v>
       </c>
       <c r="C5" t="n">
-        <v>142.0343491119073</v>
+        <v>113.1955102996573</v>
       </c>
       <c r="D5" t="n">
-        <v>92.52972112526189</v>
+        <v>100.7273144557228</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.5975498611836</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>137.6606630894878</v>
+        <v>112.5033781681633</v>
       </c>
       <c r="D6" t="n">
-        <v>42.10323204432872</v>
+        <v>42.94851681768522</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>21.91849924501429</v>
       </c>
       <c r="C7" t="n">
-        <v>134.9245322377519</v>
+        <v>99.35188592207295</v>
       </c>
       <c r="D7" t="n">
-        <v>31.62013005838127</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>95.88238953526472</v>
+        <v>68.59471209572465</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>48.92343334573128</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2268,7 +2268,7 @@
         <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.175953823238431</v>
+        <v>5.528221322613789</v>
       </c>
       <c r="C2" t="n">
-        <v>12.70774228377071</v>
+        <v>4.51211244871834</v>
       </c>
       <c r="D2" t="n">
-        <v>11.84380430403352</v>
+        <v>25.1926278386774</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06630117999905</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6691763858646</v>
+        <v>16.49827016986765</v>
       </c>
       <c r="D3" t="n">
-        <v>73.68998268076558</v>
+        <v>100.0842697094411</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.11475097487241</v>
+        <v>48.94503179522473</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0604300270987</v>
+        <v>76.00199852426682</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0152949948991</v>
+        <v>178.4228277698153</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.63177216211199</v>
+        <v>49.38190952361457</v>
       </c>
       <c r="C5" t="n">
-        <v>186.2620831882261</v>
+        <v>137.1010668980671</v>
       </c>
       <c r="D5" t="n">
-        <v>114.5454133929966</v>
+        <v>129.4188911123358</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.59504658642736</v>
+        <v>47.65796055495717</v>
       </c>
       <c r="C6" t="n">
-        <v>179.7236434779424</v>
+        <v>144.3826896204657</v>
       </c>
       <c r="D6" t="n">
-        <v>57.31835796474579</v>
+        <v>61.14226527278711</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>130.2533766609455</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>133.7680334421491</v>
+        <v>97.9686034067892</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>79.09843078346124</v>
+        <v>60.68280734719958</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.56367171762047</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2461,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>33.05151821117311</v>
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.913426275577033</v>
+        <v>3.30259927708627</v>
       </c>
       <c r="C2" t="n">
-        <v>6.040693624230625</v>
+        <v>2.097994843975434</v>
       </c>
       <c r="D2" t="n">
-        <v>8.299695091702535</v>
+        <v>17.35828115878785</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.46252634188726</v>
+        <v>24.14117604742907</v>
       </c>
       <c r="C3" t="n">
-        <v>37.99363615435156</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D3" t="n">
-        <v>70.53366381161209</v>
+        <v>100.5800523000857</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.58621085708914</v>
+        <v>53.94801809606648</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4575958789621</v>
+        <v>70.5906051784584</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4304354050753</v>
+        <v>190.0496658312103</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>220.5250780664398</v>
+        <v>160.294856410898</v>
       </c>
       <c r="D5" t="n">
-        <v>120.4358996184775</v>
+        <v>140.1935721664445</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.18874190558942</v>
+        <v>39.80888765950392</v>
       </c>
       <c r="C6" t="n">
-        <v>215.9098821087756</v>
+        <v>174.8129414612998</v>
       </c>
       <c r="D6" t="n">
-        <v>55.82904669740338</v>
+        <v>59.08943082320704</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>172.7728697318749</v>
+        <v>133.6070268186527</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>75.43749359432491</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>32.50468473990763</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2758,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>25.90832191507333</v>
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.138246499849553</v>
+        <v>4.040873550679871</v>
       </c>
       <c r="C2" t="n">
-        <v>4.711407232680442</v>
+        <v>4.606360228326034</v>
       </c>
       <c r="D2" t="n">
-        <v>15.79533881362693</v>
+        <v>21.85566739194249</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.09374905798896</v>
+        <v>17.75490723130357</v>
       </c>
       <c r="C3" t="n">
-        <v>30.80233422074368</v>
+        <v>12.9443434804942</v>
       </c>
       <c r="D3" t="n">
-        <v>62.51769380643689</v>
+        <v>91.94558124123503</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.16580185549325</v>
+        <v>50.79562621772997</v>
       </c>
       <c r="C4" t="n">
-        <v>101.7316423571672</v>
+        <v>58.44049559069988</v>
       </c>
       <c r="D4" t="n">
-        <v>149.2855376554743</v>
+        <v>195.9332798227614</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.19752088166541</v>
+        <v>64.18175616513524</v>
       </c>
       <c r="C5" t="n">
-        <v>212.76927120289</v>
+        <v>147.4094177926586</v>
       </c>
       <c r="D5" t="n">
-        <v>140.5126401703248</v>
+        <v>171.8794793210103</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.52712606838509</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="C6" t="n">
-        <v>276.2471142640803</v>
+        <v>212.0859748007342</v>
       </c>
       <c r="D6" t="n">
-        <v>74.14355012012763</v>
+        <v>81.26809320984674</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C7" t="n">
-        <v>234.2764181598248</v>
+        <v>186.965996292171</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>150.7915386337888</v>
+        <v>116.9948739150924</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>53.24999547834697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.556070111231194</v>
+        <v>2.97960428238907</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4626241528785</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="D2" t="n">
-        <v>11.67592544660732</v>
+        <v>15.851298432769</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.616218763097507</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="C3" t="n">
-        <v>25.73651606683013</v>
+        <v>15.37416904850505</v>
       </c>
       <c r="D3" t="n">
-        <v>61.68811699634833</v>
+        <v>89.01997308257954</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>45.51186007347363</v>
       </c>
       <c r="C4" t="n">
-        <v>93.04022993147022</v>
+        <v>48.66425195181014</v>
       </c>
       <c r="D4" t="n">
-        <v>147.8305875577805</v>
+        <v>197.6434843235594</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.6827252317416</v>
+        <v>70.73492209098271</v>
       </c>
       <c r="C5" t="n">
-        <v>210.4130767126977</v>
+        <v>137.223785361098</v>
       </c>
       <c r="D5" t="n">
-        <v>153.0544670920778</v>
+        <v>193.5515598922587</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.00764266411829</v>
+        <v>60.98125864929064</v>
       </c>
       <c r="C6" t="n">
-        <v>309.575485327851</v>
+        <v>230.1187166323396</v>
       </c>
       <c r="D6" t="n">
-        <v>88.91590782592939</v>
+        <v>99.18008007382979</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>291.7675637205181</v>
+        <v>229.3657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>46.11268966847268</v>
+        <v>48.98724694650735</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>192.1820218448343</v>
+        <v>153.8791351636451</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>73.21874378272709</v>
+        <v>62.45780719647781</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.243293504203962</v>
+        <v>5.019676011813941</v>
       </c>
       <c r="C2" t="n">
-        <v>7.040112787153877</v>
+        <v>8.169122647037709</v>
       </c>
       <c r="D2" t="n">
-        <v>13.4204911170539</v>
+        <v>29.29927848554181</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.564366061221674</v>
+        <v>13.24868526881071</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0374706436774</v>
+        <v>12.7283589855599</v>
       </c>
       <c r="D3" t="n">
-        <v>57.93293202760429</v>
+        <v>82.14773915285186</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.47889725768997</v>
+        <v>38.90077103307561</v>
       </c>
       <c r="C4" t="n">
-        <v>80.31579793672731</v>
+        <v>43.89099461376215</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5933644662512</v>
+        <v>196.4948395095906</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.89103567149117</v>
+        <v>69.77771807934207</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6251909700772</v>
+        <v>116.3371029532471</v>
       </c>
       <c r="D5" t="n">
-        <v>166.0380804807418</v>
+        <v>210.8548631796087</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.05797383894213</v>
+        <v>74.3045567436241</v>
       </c>
       <c r="C6" t="n">
-        <v>320.3226774462408</v>
+        <v>226.1338027008019</v>
       </c>
       <c r="D6" t="n">
-        <v>107.9951927102619</v>
+        <v>127.1952325622168</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.24840753137022</v>
+        <v>38.50709020367265</v>
       </c>
       <c r="C7" t="n">
-        <v>352.8519058787546</v>
+        <v>272.4241887037431</v>
       </c>
       <c r="D7" t="n">
-        <v>55.75443387188061</v>
+        <v>61.02445554827749</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>267.4526183294373</v>
+        <v>215.3807200961865</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>131.0171763748496</v>
+        <v>110.3828031269901</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>20.61179305066178</v>
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.289255719854315</v>
+        <v>7.297330685666541</v>
       </c>
       <c r="C2" t="n">
-        <v>7.635051895927444</v>
+        <v>5.359360717483338</v>
       </c>
       <c r="D2" t="n">
-        <v>13.53535559845077</v>
+        <v>13.1897804065559</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.622828955119977</v>
+        <v>3.592214849839079</v>
       </c>
       <c r="C2" t="n">
-        <v>4.110577637681395</v>
+        <v>4.640721397974672</v>
       </c>
       <c r="D2" t="n">
-        <v>9.98437415219006</v>
+        <v>21.56408832378119</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.47033926579223</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="C3" t="n">
-        <v>25.10328879759094</v>
+        <v>20.34672117051515</v>
       </c>
       <c r="D3" t="n">
-        <v>63.08219873637881</v>
+        <v>93.31511928865933</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.7356164345839</v>
+        <v>53.39922112939251</v>
       </c>
       <c r="C4" t="n">
-        <v>114.4560743519101</v>
+        <v>64.20924510085413</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9154187709732</v>
+        <v>200.681011720499</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.34229545807943</v>
+        <v>43.78594760940775</v>
       </c>
       <c r="C5" t="n">
-        <v>277.7118818388165</v>
+        <v>182.6787040677253</v>
       </c>
       <c r="D5" t="n">
-        <v>152.4408747769235</v>
+        <v>191.8335014098268</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.90569546713008</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="C6" t="n">
-        <v>292.0257633667351</v>
+        <v>225.9727960773054</v>
       </c>
       <c r="D6" t="n">
-        <v>83.80394752991624</v>
+        <v>97.28825224774619</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>188.0439552714341</v>
+        <v>151.4532365864512</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>96.54997797415255</v>
+        <v>81.36234098945441</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
         <v>16.52575910558656</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.356816384998097</v>
+        <v>7.097054154000192</v>
       </c>
       <c r="C2" t="n">
-        <v>7.852999886270236</v>
+        <v>3.405682786032185</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93755336202248</v>
+        <v>20.01489044647972</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.120436172452868</v>
+        <v>15.4968875115359</v>
       </c>
       <c r="C3" t="n">
-        <v>19.23734626471625</v>
+        <v>13.50393967191488</v>
       </c>
       <c r="D3" t="n">
-        <v>14.50532233024662</v>
+        <v>14.21570675749381</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39763137160295</v>
+        <v>13.39756503959892</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14054071015661</v>
+        <v>70.1401934426061</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576191926070935</v>
+        <v>1.576184122305755</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.229369109895258</v>
+        <v>5.299474107524283</v>
       </c>
       <c r="C2" t="n">
-        <v>5.269039928692631</v>
+        <v>4.129230844062084</v>
       </c>
       <c r="D2" t="n">
-        <v>17.93554880888498</v>
+        <v>26.59947229886308</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77315952705676</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35992585902686</v>
+        <v>13.36158625479909</v>
       </c>
       <c r="D3" t="n">
-        <v>30.26728172192917</v>
+        <v>27.59201922785661</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.73344765053038</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="C4" t="n">
-        <v>29.87752788334318</v>
+        <v>21.14782729718054</v>
       </c>
       <c r="D4" t="n">
-        <v>22.66659099565036</v>
+        <v>22.52620107394306</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.438601840834</v>
+        <v>15.43971706280708</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13114711202125</v>
+        <v>86.13736887671318</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250231966491368</v>
+        <v>3.250466750064648</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.132576997802325</v>
+        <v>5.577308707826131</v>
       </c>
       <c r="C2" t="n">
-        <v>8.311476064153496</v>
+        <v>8.395906366718721</v>
       </c>
       <c r="D2" t="n">
-        <v>32.856150418028</v>
+        <v>26.10172621280995</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.57542732787565</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C3" t="n">
-        <v>22.8059991696534</v>
+        <v>15.00110492089126</v>
       </c>
       <c r="D3" t="n">
-        <v>37.59111959561037</v>
+        <v>42.46549694719579</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.04947260030661</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="C4" t="n">
-        <v>51.1402196619206</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="D4" t="n">
-        <v>32.72361447795468</v>
+        <v>31.28142710041612</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.792933349861935</v>
+        <v>15.33980787885642</v>
       </c>
       <c r="C5" t="n">
-        <v>33.79666471869646</v>
+        <v>24.56823629877644</v>
       </c>
       <c r="D5" t="n">
-        <v>30.80233422074368</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73035467862577</v>
+        <v>16.73235163631622</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0551635396172</v>
+        <v>102.067344981529</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182588669656442</v>
+        <v>5.019705490894867</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.078580874068749</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="C2" t="n">
-        <v>6.322455215349459</v>
+        <v>5.411393345808419</v>
       </c>
       <c r="D2" t="n">
-        <v>25.8238916125081</v>
+        <v>34.24826866264998</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6062624173348</v>
+        <v>19.28152491140736</v>
       </c>
       <c r="C3" t="n">
-        <v>28.24979018970197</v>
+        <v>25.14255870576082</v>
       </c>
       <c r="D3" t="n">
-        <v>54.19738201294516</v>
+        <v>52.85729639664827</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.66132240423063</v>
+        <v>34.72736154232243</v>
       </c>
       <c r="C4" t="n">
-        <v>54.45852690227482</v>
+        <v>33.5021404074224</v>
       </c>
       <c r="D4" t="n">
-        <v>43.58468933003715</v>
+        <v>44.75885958431633</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.13841073076558</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>66.53795065532759</v>
+        <v>39.39262663290327</v>
       </c>
       <c r="D5" t="n">
-        <v>35.09748042682348</v>
+        <v>34.5820628820939</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.539642442166258</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>33.52962934314132</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="D6" t="n">
         <v>38.44033135978387</v>
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05089243083118</v>
+        <v>18.05777481857991</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7605839535177</v>
+        <v>117.8054833402594</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016964143610394</v>
+        <v>6.879152311839965</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.149086782325274</v>
+        <v>6.913467333306038</v>
       </c>
       <c r="C2" t="n">
-        <v>7.475027020135213</v>
+        <v>7.903069019186824</v>
       </c>
       <c r="D2" t="n">
-        <v>33.34506077474292</v>
+        <v>34.44069121268235</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17291076913446</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="C3" t="n">
-        <v>24.53878386764903</v>
+        <v>21.39719121405923</v>
       </c>
       <c r="D3" t="n">
-        <v>58.11455535288994</v>
+        <v>63.15092107567608</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.65833610338889</v>
+        <v>26.16357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>52.55688159914875</v>
+        <v>41.83619666877358</v>
       </c>
       <c r="D4" t="n">
-        <v>52.37820351697583</v>
+        <v>52.62069519992479</v>
       </c>
     </row>
     <row r="5">
@@ -5798,10 +5798,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.92318699935727</v>
+        <v>25.59907138823559</v>
       </c>
       <c r="C5" t="n">
-        <v>63.00365892003907</v>
+        <v>37.9690924617454</v>
       </c>
       <c r="D5" t="n">
         <v>34.09118902997049</v>
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>47.49695393146069</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>31.5975498611836</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>22.45747873464579</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052847885758022</v>
+        <v>7.05736817317483</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12044892898146</v>
+        <v>66.16282662351404</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408029928598764</v>
+        <v>5.293026129881123</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.061891163096554</v>
+        <v>6.3715426005618</v>
       </c>
       <c r="C2" t="n">
-        <v>6.511932522269093</v>
+        <v>4.387430490278995</v>
       </c>
       <c r="D2" t="n">
-        <v>25.63146906247573</v>
+        <v>40.15937158992003</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.07321447165778</v>
+        <v>22.61946710584651</v>
       </c>
       <c r="C3" t="n">
-        <v>27.55274931968674</v>
+        <v>27.51347941151686</v>
       </c>
       <c r="D3" t="n">
-        <v>72.07991644580082</v>
+        <v>76.82175785731292</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.69961056469625</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="C4" t="n">
-        <v>58.26181750852697</v>
+        <v>49.30238795957057</v>
       </c>
       <c r="D4" t="n">
-        <v>70.18219813349174</v>
+        <v>73.00275928779283</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.65445017030091</v>
+        <v>33.91938318172731</v>
       </c>
       <c r="C5" t="n">
-        <v>83.96397240570847</v>
+        <v>62.04645490839843</v>
       </c>
       <c r="D5" t="n">
-        <v>46.48575379608648</v>
+        <v>46.55938487390499</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.28054316370311</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C6" t="n">
-        <v>78.53098061040662</v>
+        <v>47.89947049020189</v>
       </c>
       <c r="D6" t="n">
-        <v>35.90447703971436</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>49.34656660626167</v>
+        <v>34.13536767666159</v>
       </c>
       <c r="D7" t="n">
         <v>33.17718191731671</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>25.2849121228766</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272078185182606</v>
+        <v>7.279402133633802</v>
       </c>
       <c r="C21" t="n">
-        <v>75.44781117126954</v>
+        <v>75.52379713645071</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454058638886954</v>
+        <v>6.369476866929577</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.295146206079795</v>
+        <v>5.288674882777567</v>
       </c>
       <c r="C2" t="n">
-        <v>10.48113849053895</v>
+        <v>5.312236827679491</v>
       </c>
       <c r="D2" t="n">
-        <v>22.64891953697391</v>
+        <v>40.9369157716835</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.05081420090935</v>
+        <v>22.31512531753</v>
       </c>
       <c r="C3" t="n">
-        <v>26.21266370338984</v>
+        <v>21.18120671912493</v>
       </c>
       <c r="D3" t="n">
-        <v>75.85964510715104</v>
+        <v>91.12582190818894</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.45934441906305</v>
+        <v>40.02389040673396</v>
       </c>
       <c r="C4" t="n">
-        <v>64.49002494426873</v>
+        <v>60.86541242018951</v>
       </c>
       <c r="D4" t="n">
-        <v>90.55149950120456</v>
+        <v>95.107790596614</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.09118902997049</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>96.50579932746149</v>
+        <v>78.6625348027757</v>
       </c>
       <c r="D5" t="n">
-        <v>61.18742566718247</v>
+        <v>61.80101798233672</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.13590745600934</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8404774836184</v>
+        <v>75.75361635509239</v>
       </c>
       <c r="D6" t="n">
-        <v>42.02272873258048</v>
+        <v>42.66675522656639</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>84.3802334323091</v>
+        <v>53.05953642372311</v>
       </c>
       <c r="D7" t="n">
         <v>36.35117224514665</v>
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>46.98153638673111</v>
+        <v>35.38218726105504</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>18.82992096745382</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.478303790513456</v>
+        <v>7.488266350326342</v>
       </c>
       <c r="C21" t="n">
-        <v>84.13091764327639</v>
+        <v>84.24299644117136</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543515816699274</v>
+        <v>7.488266350326342</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617501228</v>
+        <v>10.84497616596927</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907139414</v>
+        <v>37.78907136262983</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.050912011900593</v>
+        <v>5.109996800604648</v>
       </c>
       <c r="C2" t="n">
-        <v>5.222897786593031</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="D2" t="n">
-        <v>30.02871702979719</v>
+        <v>23.92322805708628</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.97365704290136</v>
+        <v>14.55440971545896</v>
       </c>
       <c r="C3" t="n">
-        <v>20.82777754559608</v>
+        <v>27.50857067299563</v>
       </c>
       <c r="D3" t="n">
-        <v>101.2083708308037</v>
+        <v>59.56754195517522</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.33845058272045</v>
+        <v>32.17481751128071</v>
       </c>
       <c r="C4" t="n">
-        <v>56.00281604105505</v>
+        <v>74.3428449040897</v>
       </c>
       <c r="D4" t="n">
-        <v>115.8089226883622</v>
+        <v>84.39986838639405</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.05717201768713</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="C5" t="n">
-        <v>96.55488671267382</v>
+        <v>104.9242858913779</v>
       </c>
       <c r="D5" t="n">
-        <v>80.84692344472485</v>
+        <v>65.0407854063512</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.81896717845365</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>100.9914045881652</v>
+        <v>126.9537226269721</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>45.40386782600649</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="C7" t="n">
-        <v>81.14635649452011</v>
+        <v>118.5754877189298</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.19040230136165</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>53.49052366588747</v>
+        <v>77.77405313043232</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>43.26562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682669344414701</v>
+        <v>7.687674828136776</v>
       </c>
       <c r="C21" t="n">
-        <v>93.15236580102825</v>
+        <v>94.1740166446755</v>
       </c>
       <c r="D21" t="n">
-        <v>8.643003012466538</v>
+        <v>7.687674828136776</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.920159640786519</v>
+        <v>6.272386082432871</v>
       </c>
       <c r="C2" t="n">
-        <v>8.805295159389642</v>
+        <v>6.110397711232148</v>
       </c>
       <c r="D2" t="n">
-        <v>37.75212621910685</v>
+        <v>32.14241983704057</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.71135047941821</v>
+        <v>15.77668560724624</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43998720241859</v>
+        <v>20.50870954171587</v>
       </c>
       <c r="D3" t="n">
-        <v>101.0611086751667</v>
+        <v>63.7301522211817</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.70482240285375</v>
+        <v>29.97962964458485</v>
       </c>
       <c r="C4" t="n">
-        <v>53.94801809606648</v>
+        <v>70.71823238001049</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3313766979376</v>
+        <v>92.51695840510666</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.42594930158544</v>
+        <v>44.59588946541137</v>
       </c>
       <c r="C5" t="n">
-        <v>98.73927535462298</v>
+        <v>120.6322491593268</v>
       </c>
       <c r="D5" t="n">
-        <v>99.40195505498957</v>
+        <v>78.93251542144357</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.12339108222817</v>
+        <v>47.73846386670541</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8669279183708</v>
+        <v>144.7852061792069</v>
       </c>
       <c r="D6" t="n">
-        <v>63.03409309887072</v>
+        <v>54.17872880656449</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.85507085933252</v>
+        <v>37.24947139453248</v>
       </c>
       <c r="C7" t="n">
-        <v>110.7902284242525</v>
+        <v>150.195617777311</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.86905200690345</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="C8" t="n">
-        <v>79.10923000820797</v>
+        <v>114.658314378985</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>68.55936917837174</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.862905631771452</v>
+        <v>7.869157979269335</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2349100090574</v>
+        <v>103.28269847791</v>
       </c>
       <c r="D21" t="n">
-        <v>9.828632039714314</v>
+        <v>8.852802726678002</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.56025914395544</v>
+        <v>8.982009746154068</v>
       </c>
       <c r="C2" t="n">
-        <v>5.168901662859456</v>
+        <v>15.48707003449343</v>
       </c>
       <c r="D2" t="n">
-        <v>29.9786478968806</v>
+        <v>33.48545069645021</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0247489812512</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>26.79680358741669</v>
+        <v>21.87333885061894</v>
       </c>
       <c r="D3" t="n">
-        <v>106.6227094197248</v>
+        <v>71.96210672129119</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.57719520130167</v>
+        <v>29.36701907713484</v>
       </c>
       <c r="C4" t="n">
-        <v>52.46754255806228</v>
+        <v>61.55459930857077</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0813341329909</v>
+        <v>100.9403537075443</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.43224069843842</v>
+        <v>44.52225838759286</v>
       </c>
       <c r="C5" t="n">
-        <v>97.83115872819468</v>
+        <v>123.4547738090364</v>
       </c>
       <c r="D5" t="n">
-        <v>118.8651032916826</v>
+        <v>90.02626447943253</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.21397391292614</v>
+        <v>52.97117913034091</v>
       </c>
       <c r="C6" t="n">
-        <v>139.5927425714455</v>
+        <v>163.9449943752876</v>
       </c>
       <c r="D6" t="n">
-        <v>76.5989011284489</v>
+        <v>64.28189443096842</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.91602133245383</v>
+        <v>45.99291644855457</v>
       </c>
       <c r="C7" t="n">
-        <v>140.3742137440259</v>
+        <v>176.9649324290088</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>46.77144237802229</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.29873870619407</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="C8" t="n">
-        <v>107.7320843255237</v>
+        <v>150.5411929692059</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.9718734739421</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>99.84374152190058</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>58.2225476003571</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.91549724863931</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.027494862456749</v>
+        <v>8.034989655557817</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3746175009732</v>
+        <v>111.4854814708647</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03780543587803</v>
+        <v>10.04373706944727</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.72577359534565</v>
+        <v>7.954119899807657</v>
       </c>
       <c r="C2" t="n">
-        <v>3.514656781203581</v>
+        <v>10.53120762345553</v>
       </c>
       <c r="D2" t="n">
-        <v>24.80091050468292</v>
+        <v>27.34069181556942</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.95664853675967</v>
+        <v>21.03885330200914</v>
       </c>
       <c r="C3" t="n">
-        <v>36.95789232637118</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="D3" t="n">
-        <v>115.875681532251</v>
+        <v>78.24529202847079</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59300097556086</v>
+        <v>21.3903189801295</v>
       </c>
       <c r="C4" t="n">
-        <v>78.04403374910019</v>
+        <v>95.89907924623694</v>
       </c>
       <c r="D4" t="n">
-        <v>140.032565542948</v>
+        <v>98.2474197547953</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>29.82058651649687</v>
       </c>
       <c r="C5" t="n">
-        <v>83.39946747576656</v>
+        <v>97.95387719122553</v>
       </c>
       <c r="D5" t="n">
-        <v>77.70533079113505</v>
+        <v>62.61095983834034</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>28.53842401475054</v>
       </c>
       <c r="C6" t="n">
-        <v>92.45805354285189</v>
+        <v>116.5285437555752</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.35577788403162</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>75.75656159820512</v>
+        <v>105.819639797651</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>52.32224389783376</v>
+        <v>73.60162538738336</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.47068342315751</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.282784396552087</v>
+        <v>4.659374604355362</v>
       </c>
       <c r="C2" t="n">
-        <v>2.305143609571511</v>
+        <v>4.375649517828034</v>
       </c>
       <c r="D2" t="n">
-        <v>16.93612964596172</v>
+        <v>19.26483520043516</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.59125846433061</v>
+        <v>24.55351008321273</v>
       </c>
       <c r="C3" t="n">
-        <v>25.40272184738622</v>
+        <v>41.40520942660923</v>
       </c>
       <c r="D3" t="n">
-        <v>110.3042633106504</v>
+        <v>81.68631773185587</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="C4" t="n">
-        <v>87.89685370892118</v>
+        <v>101.1828453904933</v>
       </c>
       <c r="D4" t="n">
-        <v>163.2224280649619</v>
+        <v>113.2946668177862</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.91433557448583</v>
+        <v>32.44676162535709</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1955102996573</v>
+        <v>136.2911250420635</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7273144557228</v>
+        <v>77.65624340592271</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>34.01264921363075</v>
       </c>
       <c r="C6" t="n">
-        <v>112.5033781681633</v>
+        <v>137.741166401236</v>
       </c>
       <c r="D6" t="n">
-        <v>42.94851681768522</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.91849924501429</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>99.35188592207295</v>
+        <v>133.6070268186527</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>68.59471209572465</v>
+        <v>96.04928664498669</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
         <v>28.6218725696115</v>
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.528221322613789</v>
+        <v>4.291219215262808</v>
       </c>
       <c r="C2" t="n">
-        <v>4.51211244871834</v>
+        <v>7.283586217807087</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1926278386774</v>
+        <v>22.50656611985812</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.20008090968388</v>
+        <v>20.14546289114455</v>
       </c>
       <c r="C3" t="n">
-        <v>16.49827016986765</v>
+        <v>28.57376693210342</v>
       </c>
       <c r="D3" t="n">
-        <v>100.0842697094411</v>
+        <v>78.95705911404973</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.94503179522473</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>76.00199852426682</v>
+        <v>102.2421511633756</v>
       </c>
       <c r="D4" t="n">
-        <v>178.4228277698153</v>
+        <v>126.0190988125291</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.38190952361457</v>
+        <v>38.04272353956391</v>
       </c>
       <c r="C5" t="n">
-        <v>137.1010668980671</v>
+        <v>160.8593613408399</v>
       </c>
       <c r="D5" t="n">
-        <v>129.4188911123358</v>
+        <v>96.82486733134169</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.65796055495717</v>
+        <v>38.7220929509027</v>
       </c>
       <c r="C6" t="n">
-        <v>144.3826896204657</v>
+        <v>176.4230076962646</v>
       </c>
       <c r="D6" t="n">
-        <v>61.14226527278711</v>
+        <v>50.51582812201963</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.93763547748049</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>130.2533766609455</v>
+        <v>164.2689711176891</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>97.9686034067892</v>
+        <v>134.9363132102029</v>
       </c>
       <c r="D8" t="n">
         <v>29.79113408536946</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>79.76405572694058</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2450,7 +2450,7 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
         <v>30.60598467989432</v>
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.30259927708627</v>
+        <v>2.541744806294992</v>
       </c>
       <c r="C2" t="n">
-        <v>2.097994843975434</v>
+        <v>3.39193831817273</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35828115878785</v>
+        <v>15.73348870825938</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.14117604742907</v>
+        <v>19.73803759388213</v>
       </c>
       <c r="C3" t="n">
-        <v>18.05434028109884</v>
+        <v>30.33600406122644</v>
       </c>
       <c r="D3" t="n">
-        <v>100.5800523000857</v>
+        <v>80.68002633500288</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.94801809606648</v>
+        <v>42.42328179591317</v>
       </c>
       <c r="C4" t="n">
-        <v>70.5906051784584</v>
+        <v>100.799963785837</v>
       </c>
       <c r="D4" t="n">
-        <v>190.0496658312103</v>
+        <v>135.565613488625</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>40.32528695193774</v>
       </c>
       <c r="C5" t="n">
-        <v>160.294856410898</v>
+        <v>191.9562198728576</v>
       </c>
       <c r="D5" t="n">
-        <v>140.1935721664445</v>
+        <v>102.2981107825177</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>32.8453511932813</v>
       </c>
       <c r="C6" t="n">
-        <v>174.8129414612998</v>
+        <v>214.0583059385661</v>
       </c>
       <c r="D6" t="n">
-        <v>59.08943082320704</v>
+        <v>49.71079500453725</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>133.6070268186527</v>
+        <v>174.9287876904009</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>75.43749359432491</v>
+        <v>99.72102305886976</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
         <v>31.94999728700819</v>
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.040873550679871</v>
+        <v>3.28394607070558</v>
       </c>
       <c r="C2" t="n">
-        <v>4.606360228326034</v>
+        <v>4.909720268938299</v>
       </c>
       <c r="D2" t="n">
-        <v>21.85566739194249</v>
+        <v>14.39340309196249</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.75490723130357</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9443434804942</v>
+        <v>21.63281066307847</v>
       </c>
       <c r="D3" t="n">
-        <v>91.94558124123503</v>
+        <v>75.75656159820512</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.79562621772997</v>
+        <v>40.17704304859647</v>
       </c>
       <c r="C4" t="n">
-        <v>58.44049559069988</v>
+        <v>88.38183707481912</v>
       </c>
       <c r="D4" t="n">
-        <v>195.9332798227614</v>
+        <v>142.8403639770939</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.18175616513524</v>
+        <v>50.33911353525522</v>
       </c>
       <c r="C5" t="n">
-        <v>147.4094177926586</v>
+        <v>190.6554041647306</v>
       </c>
       <c r="D5" t="n">
-        <v>171.8794793210103</v>
+        <v>121.9821522526662</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>212.0859748007342</v>
+        <v>256.7250611651325</v>
       </c>
       <c r="D6" t="n">
-        <v>81.26809320984674</v>
+        <v>64.92592092495433</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>186.965996292171</v>
+        <v>235.9532432386784</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9948739150924</v>
+        <v>153.7956866087841</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>53.24999547834697</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
         <v>23.81130881880213</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.97960428238907</v>
+        <v>2.176534660315179</v>
       </c>
       <c r="C2" t="n">
-        <v>2.562361508084175</v>
+        <v>2.54861704022472</v>
       </c>
       <c r="D2" t="n">
-        <v>15.851298432769</v>
+        <v>11.71912234559418</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>13.19468914507713</v>
       </c>
       <c r="C3" t="n">
-        <v>15.37416904850505</v>
+        <v>20.88177366932966</v>
       </c>
       <c r="D3" t="n">
-        <v>89.01997308257954</v>
+        <v>71.17670855789376</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.51186007347363</v>
+        <v>36.27165068110266</v>
       </c>
       <c r="C4" t="n">
-        <v>48.66425195181014</v>
+        <v>75.27452347541994</v>
       </c>
       <c r="D4" t="n">
-        <v>197.6434843235594</v>
+        <v>147.1414006693992</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.73492209098271</v>
+        <v>54.92878405260905</v>
       </c>
       <c r="C5" t="n">
-        <v>137.223785361098</v>
+        <v>186.4584327290755</v>
       </c>
       <c r="D5" t="n">
-        <v>193.5515598922587</v>
+        <v>138.2055330653448</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.98125864929064</v>
+        <v>49.34853010167018</v>
       </c>
       <c r="C6" t="n">
-        <v>230.1187166323396</v>
+        <v>284.7402136535194</v>
       </c>
       <c r="D6" t="n">
-        <v>99.18008007382979</v>
+        <v>77.08192099893833</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>229.3657161431823</v>
+        <v>287.8150474632204</v>
       </c>
       <c r="D7" t="n">
-        <v>48.98724694650735</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>153.8791351636451</v>
+        <v>197.1889351364931</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>62.45780719647781</v>
+        <v>77.54530591534278</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.019676011813941</v>
+        <v>3.856304982281471</v>
       </c>
       <c r="C2" t="n">
-        <v>8.169122647037709</v>
+        <v>12.75486617357456</v>
       </c>
       <c r="D2" t="n">
-        <v>29.29927848554181</v>
+        <v>15.73741569907637</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.24868526881071</v>
+        <v>10.41143440353742</v>
       </c>
       <c r="C3" t="n">
-        <v>12.7283589855599</v>
+        <v>15.81104677689488</v>
       </c>
       <c r="D3" t="n">
-        <v>82.14773915285186</v>
+        <v>65.10950774564847</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.90077103307561</v>
+        <v>31.21761349964007</v>
       </c>
       <c r="C4" t="n">
-        <v>43.89099461376215</v>
+        <v>64.83461838845936</v>
       </c>
       <c r="D4" t="n">
-        <v>196.4948395095906</v>
+        <v>148.1241301213502</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.77771807934207</v>
+        <v>54.60971604872884</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3371029532471</v>
+        <v>165.7435561694678</v>
       </c>
       <c r="D5" t="n">
-        <v>210.8548631796087</v>
+        <v>153.4471661737765</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.3045567436241</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="C6" t="n">
-        <v>226.1338027008019</v>
+        <v>290.4156971317702</v>
       </c>
       <c r="D6" t="n">
-        <v>127.1952325622168</v>
+        <v>94.75239792767668</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.50709020367265</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>272.4241887037431</v>
+        <v>338.2395730487451</v>
       </c>
       <c r="D7" t="n">
-        <v>61.02445554827749</v>
+        <v>51.86180422454201</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>215.3807200961865</v>
+        <v>270.9574576335984</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>110.3828031269901</v>
+        <v>137.8953007908027</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>52.52841091572559</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>19.96089432274615</v>
+      </c>
+      <c r="D12" t="n">
         <v>20.17786056538469</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.297330685666541</v>
+        <v>5.373105185342792</v>
       </c>
       <c r="C2" t="n">
-        <v>5.359360717483338</v>
+        <v>8.078801858247003</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1897804065559</v>
+        <v>6.665085164131596</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.592214849839079</v>
+        <v>2.755765805820797</v>
       </c>
       <c r="C2" t="n">
-        <v>4.640721397974672</v>
+        <v>7.347399818583129</v>
       </c>
       <c r="D2" t="n">
-        <v>21.56408832378119</v>
+        <v>11.58265941470387</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.21141991377833</v>
+        <v>14.45132620651305</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34672117051515</v>
+        <v>27.94544840138546</v>
       </c>
       <c r="D3" t="n">
-        <v>93.31511928865933</v>
+        <v>71.36814936022188</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.39922112939251</v>
+        <v>41.93829843001524</v>
       </c>
       <c r="C4" t="n">
-        <v>64.20924510085413</v>
+        <v>93.48692513690251</v>
       </c>
       <c r="D4" t="n">
-        <v>200.681011720499</v>
+        <v>151.3913864810837</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.78594760940775</v>
+        <v>34.53297549688156</v>
       </c>
       <c r="C5" t="n">
-        <v>182.6787040677253</v>
+        <v>245.4369260617026</v>
       </c>
       <c r="D5" t="n">
-        <v>191.8335014098268</v>
+        <v>138.7700379952867</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.90948358922682</v>
+        <v>18.95852991671016</v>
       </c>
       <c r="C6" t="n">
-        <v>225.9727960773054</v>
+        <v>279.7087566692545</v>
       </c>
       <c r="D6" t="n">
-        <v>97.28825224774619</v>
+        <v>76.11588125795947</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.066619975168541</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>151.4532365864512</v>
+        <v>190.5591928897144</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>81.36234098945441</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>40.04843409934012</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>15.99267010218054</v>
+      </c>
+      <c r="D11" t="n">
         <v>16.17036643664921</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.097054154000192</v>
+        <v>6.275331325545611</v>
       </c>
       <c r="C2" t="n">
-        <v>3.405682786032185</v>
+        <v>4.984333094461056</v>
       </c>
       <c r="D2" t="n">
-        <v>20.01489044647972</v>
+        <v>14.84108004509903</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4968875115359</v>
+        <v>11.41772580039041</v>
       </c>
       <c r="C3" t="n">
-        <v>13.50393967191488</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="D3" t="n">
-        <v>14.21570675749381</v>
+        <v>8.732645829275379</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39756503959892</v>
+        <v>13.39854868766088</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1401934426061</v>
+        <v>70.14534312951872</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576184122305755</v>
+        <v>1.576299845607162</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.299474107524283</v>
+        <v>4.513094196422587</v>
       </c>
       <c r="C2" t="n">
-        <v>4.129230844062084</v>
+        <v>7.730281423239385</v>
       </c>
       <c r="D2" t="n">
-        <v>26.59947229886308</v>
+        <v>27.98766355266807</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9455872701057</v>
+        <v>17.56346642897544</v>
       </c>
       <c r="C3" t="n">
-        <v>13.36158625479909</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="D3" t="n">
-        <v>27.59201922785661</v>
+        <v>19.08517537055799</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.9443845382232</v>
+        <v>13.32427984203771</v>
       </c>
       <c r="C4" t="n">
-        <v>21.14782729718054</v>
+        <v>31.5494442236755</v>
       </c>
       <c r="D4" t="n">
-        <v>22.52620107394306</v>
+        <v>19.64182631886593</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43971706280708</v>
+        <v>15.44215663078099</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13736887671318</v>
+        <v>86.15097909804129</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250466750064648</v>
+        <v>3.250980343322313</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.577308707826131</v>
+        <v>5.040292713603124</v>
       </c>
       <c r="C2" t="n">
-        <v>8.395906366718721</v>
+        <v>6.935065782799468</v>
       </c>
       <c r="D2" t="n">
-        <v>26.10172621280995</v>
+        <v>20.80028860987717</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48769192929919</v>
+        <v>16.47372647726148</v>
       </c>
       <c r="C3" t="n">
-        <v>15.00110492089126</v>
+        <v>26.02613163958294</v>
       </c>
       <c r="D3" t="n">
-        <v>42.46549694719579</v>
+        <v>37.04624961975339</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>25.07874510498477</v>
       </c>
       <c r="C4" t="n">
-        <v>28.39705234533899</v>
+        <v>42.15526467265379</v>
       </c>
       <c r="D4" t="n">
-        <v>31.28142710041612</v>
+        <v>24.79796526157018</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.33980787885642</v>
+        <v>11.78097245096173</v>
       </c>
       <c r="C5" t="n">
-        <v>24.56823629877644</v>
+        <v>35.51472320112837</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>29.50151851261666</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73235163631622</v>
+        <v>16.73453178459485</v>
       </c>
       <c r="C21" t="n">
-        <v>102.067344981529</v>
+        <v>102.0806438860286</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019705490894867</v>
+        <v>4.183632946148713</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.215845626214056</v>
+        <v>5.324017800130453</v>
       </c>
       <c r="C2" t="n">
-        <v>5.411393345808419</v>
+        <v>6.252751128347935</v>
       </c>
       <c r="D2" t="n">
-        <v>34.24826866264998</v>
+        <v>19.91082518982956</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.28152491140736</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C3" t="n">
-        <v>25.14255870576082</v>
+        <v>26.52682296874882</v>
       </c>
       <c r="D3" t="n">
-        <v>52.85729639664827</v>
+        <v>44.61061568097507</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.72736154232243</v>
+        <v>28.89479843139213</v>
       </c>
       <c r="C4" t="n">
-        <v>33.5021404074224</v>
+        <v>54.98179842863836</v>
       </c>
       <c r="D4" t="n">
-        <v>44.75885958431633</v>
+        <v>37.088464771036</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>24.56823629877644</v>
       </c>
       <c r="C5" t="n">
-        <v>39.39262663290327</v>
+        <v>58.04583301359268</v>
       </c>
       <c r="D5" t="n">
-        <v>34.5820628820939</v>
+        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.4038014060817</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>26.28433128579986</v>
+        <v>35.50196048097316</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05777481857991</v>
+        <v>18.05960393198509</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8054833402594</v>
+        <v>117.8174161277122</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879152311839965</v>
+        <v>6.019867977328363</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.913467333306038</v>
+        <v>5.396667130244716</v>
       </c>
       <c r="C2" t="n">
-        <v>7.903069019186824</v>
+        <v>7.220754364735291</v>
       </c>
       <c r="D2" t="n">
-        <v>34.44069121268235</v>
+        <v>22.81778014210436</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89511722656161</v>
+        <v>15.7128720064702</v>
       </c>
       <c r="C3" t="n">
-        <v>21.39719121405923</v>
+        <v>23.7141157960817</v>
       </c>
       <c r="D3" t="n">
-        <v>63.15092107567608</v>
+        <v>46.87354413926396</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.16357631817749</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="C4" t="n">
-        <v>41.83619666877358</v>
+        <v>51.34442318440394</v>
       </c>
       <c r="D4" t="n">
-        <v>52.62069519992479</v>
+        <v>43.94204549438299</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.59907138823559</v>
+        <v>20.98485717827558</v>
       </c>
       <c r="C5" t="n">
-        <v>37.9690924617454</v>
+        <v>60.05841580729864</v>
       </c>
       <c r="D5" t="n">
-        <v>34.09118902997049</v>
+        <v>30.01693605734623</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93336432929824</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>30.71201343195298</v>
+        <v>44.19631814978292</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5975498611836</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.05736817317483</v>
+        <v>7.058201783285456</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16282662351404</v>
+        <v>66.17064171830116</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293026129881123</v>
+        <v>4.41137611455341</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.3715426005618</v>
+        <v>4.837070938824034</v>
       </c>
       <c r="C2" t="n">
-        <v>4.387430490278995</v>
+        <v>9.8341667534403</v>
       </c>
       <c r="D2" t="n">
-        <v>40.15937158992003</v>
+        <v>19.87450052477243</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61946710584651</v>
+        <v>17.7303635386974</v>
       </c>
       <c r="C3" t="n">
-        <v>27.51347941151686</v>
+        <v>26.61518026213103</v>
       </c>
       <c r="D3" t="n">
-        <v>76.82175785731292</v>
+        <v>54.71279955767474</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.28066633689012</v>
+        <v>27.82272993835461</v>
       </c>
       <c r="C4" t="n">
-        <v>49.30238795957057</v>
+        <v>56.01557876121026</v>
       </c>
       <c r="D4" t="n">
-        <v>73.00275928779283</v>
+        <v>57.89169862402591</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.91938318172731</v>
+        <v>28.44613973055134</v>
       </c>
       <c r="C5" t="n">
-        <v>62.04645490839843</v>
+        <v>81.82867114897165</v>
       </c>
       <c r="D5" t="n">
-        <v>46.55938487390499</v>
+        <v>40.07985002587604</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.1635763181775</v>
+        <v>21.65539086027615</v>
       </c>
       <c r="C6" t="n">
-        <v>47.89947049020189</v>
+        <v>74.90833158173589</v>
       </c>
       <c r="D6" t="n">
-        <v>35.783722072092</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>34.13536767666159</v>
+        <v>47.37030847761284</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.279402133633802</v>
+        <v>7.280939647372778</v>
       </c>
       <c r="C21" t="n">
-        <v>75.52379713645071</v>
+        <v>75.53974884149258</v>
       </c>
       <c r="D21" t="n">
-        <v>6.369476866929577</v>
+        <v>5.460704735529584</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.288674882777567</v>
+        <v>3.535273482992764</v>
       </c>
       <c r="C2" t="n">
-        <v>5.312236827679491</v>
+        <v>5.891467973185108</v>
       </c>
       <c r="D2" t="n">
-        <v>40.9369157716835</v>
+        <v>19.12444527872787</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.31512531753</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C3" t="n">
-        <v>21.18120671912493</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D3" t="n">
-        <v>91.12582190818894</v>
+        <v>57.91820581204058</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.02389040673396</v>
+        <v>31.56220694383071</v>
       </c>
       <c r="C4" t="n">
-        <v>60.86541242018951</v>
+        <v>62.30759979772807</v>
       </c>
       <c r="D4" t="n">
-        <v>95.107790596614</v>
+        <v>72.32633511956676</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C5" t="n">
-        <v>78.6625348027757</v>
+        <v>93.48692513690253</v>
       </c>
       <c r="D5" t="n">
-        <v>61.80101798233672</v>
+        <v>51.46812339513905</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>75.75361635509239</v>
+        <v>105.9021066048077</v>
       </c>
       <c r="D6" t="n">
-        <v>42.66675522656639</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>53.05953642372311</v>
+        <v>81.20624310447916</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>35.38218726105504</v>
+        <v>46.39739650270425</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.488266350326342</v>
+        <v>7.491242087579725</v>
       </c>
       <c r="C21" t="n">
-        <v>84.24299644117136</v>
+        <v>85.21287874621937</v>
       </c>
       <c r="D21" t="n">
-        <v>7.488266350326342</v>
+        <v>6.554836826632259</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_27_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497616596927</v>
+        <v>10.84497637063663</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907136262983</v>
+        <v>37.78907207578857</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.109996800604648</v>
+        <v>0.68329640215578</v>
       </c>
       <c r="C2" t="n">
-        <v>3.653083207502381</v>
+        <v>4.001603642509999</v>
       </c>
       <c r="D2" t="n">
-        <v>23.92322805708628</v>
+        <v>10.8198414485041</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.55440971545896</v>
+        <v>5.654866776461628</v>
       </c>
       <c r="C3" t="n">
-        <v>27.50857067299563</v>
+        <v>48.86649197888499</v>
       </c>
       <c r="D3" t="n">
-        <v>59.56754195517522</v>
+        <v>62.36552291227864</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.17481751128071</v>
+        <v>10.18465068385641</v>
       </c>
       <c r="C4" t="n">
-        <v>74.3428449040897</v>
+        <v>134.5445958762084</v>
       </c>
       <c r="D4" t="n">
-        <v>84.39986838639405</v>
+        <v>76.52527005063037</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.72427743048944</v>
+        <v>10.30835089459151</v>
       </c>
       <c r="C5" t="n">
-        <v>104.9242858913779</v>
+        <v>151.066427990978</v>
       </c>
       <c r="D5" t="n">
-        <v>65.0407854063512</v>
+        <v>46.78027810736052</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>7.3258013690897</v>
       </c>
       <c r="C6" t="n">
-        <v>126.9537226269721</v>
+        <v>108.5989675483737</v>
       </c>
       <c r="D6" t="n">
-        <v>45.40386782600649</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.84727363096077</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>118.5754877189298</v>
+        <v>57.01205268102077</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>77.77405313043232</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687674828136776</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.1740166446755</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.687674828136776</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.272386082432871</v>
+        <v>0.828595062384308</v>
       </c>
       <c r="C2" t="n">
-        <v>6.110397711232148</v>
+        <v>4.181263472387165</v>
       </c>
       <c r="D2" t="n">
-        <v>32.14241983704057</v>
+        <v>11.62781980909922</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.77668560724624</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C3" t="n">
-        <v>20.50870954171587</v>
+        <v>30.0709321810798</v>
       </c>
       <c r="D3" t="n">
-        <v>63.7301522211817</v>
+        <v>56.71556487433824</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.97962964458485</v>
+        <v>10.66963404975434</v>
       </c>
       <c r="C4" t="n">
-        <v>70.71823238001049</v>
+        <v>127.7803541939479</v>
       </c>
       <c r="D4" t="n">
-        <v>92.51695840510666</v>
+        <v>89.81126173220245</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.59588946541137</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6322491593268</v>
+        <v>204.1544350981243</v>
       </c>
       <c r="D5" t="n">
-        <v>78.93251542144357</v>
+        <v>62.68459091615885</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.73846386670541</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>144.7852061792069</v>
+        <v>175.2959613317893</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>37.31328499530853</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.24947139453248</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>150.195617777311</v>
+        <v>105.6998665777328</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>68.55936917837174</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>40.71307729511523</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869157979269335</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.28269847791</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.852802726678002</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.982009746154068</v>
+        <v>0.450622196249286</v>
       </c>
       <c r="C2" t="n">
-        <v>15.48707003449343</v>
+        <v>1.821141991377833</v>
       </c>
       <c r="D2" t="n">
-        <v>33.48545069645021</v>
+        <v>7.952156404399163</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>3.818998569520093</v>
       </c>
       <c r="C3" t="n">
-        <v>21.87333885061894</v>
+        <v>25.58925391119311</v>
       </c>
       <c r="D3" t="n">
-        <v>71.96210672129119</v>
+        <v>55.43438412029615</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.36701907713484</v>
+        <v>11.60131262108456</v>
       </c>
       <c r="C4" t="n">
-        <v>61.55459930857077</v>
+        <v>119.2931452907342</v>
       </c>
       <c r="D4" t="n">
-        <v>100.9403537075443</v>
+        <v>97.46889382532758</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.52225838759286</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C5" t="n">
-        <v>123.4547738090364</v>
+        <v>241.7553721707771</v>
       </c>
       <c r="D5" t="n">
-        <v>90.02626447943253</v>
+        <v>70.68583470577036</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.97117913034091</v>
+        <v>8.895615948180351</v>
       </c>
       <c r="C6" t="n">
-        <v>163.9449943752876</v>
+        <v>217.4394450319921</v>
       </c>
       <c r="D6" t="n">
-        <v>64.28189443096842</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.99291644855457</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9649324290088</v>
+        <v>97.6750608432194</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.70768553050848</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>150.5411929692059</v>
+        <v>43.47669708257</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>99.84374152190058</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.034989655557817</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.4854814708647</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04373706944727</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.954119899807657</v>
+        <v>0.4103705403751667</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53120762345553</v>
+        <v>7.515278676009333</v>
       </c>
       <c r="D2" t="n">
-        <v>27.34069181556942</v>
+        <v>8.948630324209677</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.03885330200914</v>
+        <v>2.680171232593793</v>
       </c>
       <c r="C3" t="n">
-        <v>39.83441309981433</v>
+        <v>15.47725255745097</v>
       </c>
       <c r="D3" t="n">
-        <v>78.24529202847079</v>
+        <v>49.36227456952963</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.3903189801295</v>
+        <v>9.674141877648069</v>
       </c>
       <c r="C4" t="n">
-        <v>95.89907924623694</v>
+        <v>91.10029646787852</v>
       </c>
       <c r="D4" t="n">
-        <v>98.2474197547953</v>
+        <v>103.492897738586</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.82058651649687</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C5" t="n">
-        <v>97.95387719122553</v>
+        <v>233.1159923734052</v>
       </c>
       <c r="D5" t="n">
-        <v>62.61095983834034</v>
+        <v>86.46742905153783</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="C6" t="n">
-        <v>116.5285437555752</v>
+        <v>300.3176044768036</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>105.819639797651</v>
+        <v>194.6913689768892</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>73.60162538738336</v>
+        <v>79.69336989223483</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.659374604355362</v>
+        <v>0.2739076094848601</v>
       </c>
       <c r="C2" t="n">
-        <v>4.375649517828034</v>
+        <v>3.528401249063037</v>
       </c>
       <c r="D2" t="n">
-        <v>19.26483520043516</v>
+        <v>7.200137662946108</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.55351008321273</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C3" t="n">
-        <v>41.40520942660923</v>
+        <v>22.45256999612455</v>
       </c>
       <c r="D3" t="n">
-        <v>81.68631773185587</v>
+        <v>46.00469742100554</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.50740899884213</v>
+        <v>8.129852738867836</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1828453904933</v>
+        <v>69.36538404355839</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2946668177862</v>
+        <v>104.9095596758142</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.44676162535709</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C5" t="n">
-        <v>136.2911250420635</v>
+        <v>214.4136986075034</v>
       </c>
       <c r="D5" t="n">
-        <v>77.65624340592271</v>
+        <v>99.52467351802042</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.01264921363075</v>
+        <v>14.85286101755</v>
       </c>
       <c r="C6" t="n">
-        <v>137.741166401236</v>
+        <v>340.3277504156781</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>58.32464936159877</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>133.6070268186527</v>
+        <v>279.0117157992393</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>96.04928664498669</v>
+        <v>121.0004045484194</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
+        <v>31.74481201682062</v>
+      </c>
+      <c r="D10" t="n">
         <v>33.02599277086271</v>
-      </c>
-      <c r="D10" t="n">
-        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.291219215262808</v>
+        <v>0.4997095814616265</v>
       </c>
       <c r="C2" t="n">
-        <v>7.283586217807087</v>
+        <v>4.596542751283566</v>
       </c>
       <c r="D2" t="n">
-        <v>22.50656611985812</v>
+        <v>12.07058802371453</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14546289114455</v>
+        <v>1.55116137270996</v>
       </c>
       <c r="C3" t="n">
-        <v>28.57376693210342</v>
+        <v>18.19669369821463</v>
       </c>
       <c r="D3" t="n">
-        <v>78.95705911404973</v>
+        <v>41.7046424764045</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>6.279258316362599</v>
       </c>
       <c r="C4" t="n">
-        <v>102.2421511633756</v>
+        <v>62.95849852564371</v>
       </c>
       <c r="D4" t="n">
-        <v>126.0190988125291</v>
+        <v>103.9778811044839</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.04272353956391</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C5" t="n">
-        <v>160.8593613408399</v>
+        <v>174.9474408967816</v>
       </c>
       <c r="D5" t="n">
-        <v>96.82486733134169</v>
+        <v>111.2074711985575</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.7220929509027</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="C6" t="n">
-        <v>176.4230076962646</v>
+        <v>341.8975649947688</v>
       </c>
       <c r="D6" t="n">
-        <v>50.51582812201963</v>
+        <v>71.64794745593223</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>372.9738068249972</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>44.85507085933252</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>134.9363132102029</v>
+        <v>221.8062588204818</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>79.76405572694058</v>
+        <v>86.97499261463339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.541744806294992</v>
+        <v>0.3475386873033709</v>
       </c>
       <c r="C2" t="n">
-        <v>3.39193831817273</v>
+        <v>2.501493150420873</v>
       </c>
       <c r="D2" t="n">
-        <v>15.73348870825938</v>
+        <v>8.786641953008953</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.73803759388213</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="C3" t="n">
-        <v>30.33600406122644</v>
+        <v>20.90631736193583</v>
       </c>
       <c r="D3" t="n">
-        <v>80.68002633500288</v>
+        <v>46.68210333693583</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.42328179591317</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C4" t="n">
-        <v>100.799963785837</v>
+        <v>92.98917905084939</v>
       </c>
       <c r="D4" t="n">
-        <v>135.565613488625</v>
+        <v>107.1430357029757</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.32528695193774</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>191.9562198728576</v>
+        <v>276.9019399828129</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2981107825177</v>
+        <v>102.1017612416683</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>214.0583059385661</v>
+        <v>319.356637705262</v>
       </c>
       <c r="D6" t="n">
-        <v>49.71079500453725</v>
+        <v>61.18251692866124</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>3.413536767666159</v>
       </c>
       <c r="C7" t="n">
-        <v>174.9287876904009</v>
+        <v>155.9447323333803</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>64.08849013323177</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.28394607070558</v>
+        <v>0.1688606051304514</v>
       </c>
       <c r="C2" t="n">
-        <v>4.909720268938299</v>
+        <v>1.282162501746335</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39340309196249</v>
+        <v>6.757369448330795</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.42187377538564</v>
+        <v>1.757328390601791</v>
       </c>
       <c r="C3" t="n">
-        <v>21.63281066307847</v>
+        <v>14.97656122828509</v>
       </c>
       <c r="D3" t="n">
-        <v>75.75656159820512</v>
+        <v>43.02509313861646</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.17704304859647</v>
+        <v>6.891868883812609</v>
       </c>
       <c r="C4" t="n">
-        <v>88.38183707481912</v>
+        <v>70.06733365209485</v>
       </c>
       <c r="D4" t="n">
-        <v>142.8403639770939</v>
+        <v>101.8337441184089</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.33911353525522</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>190.6554041647306</v>
+        <v>204.1053477129119</v>
       </c>
       <c r="D5" t="n">
-        <v>121.9821522526662</v>
+        <v>103.50075172022</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>6.198755004614362</v>
       </c>
       <c r="C6" t="n">
-        <v>256.7250611651325</v>
+        <v>310.6220283805781</v>
       </c>
       <c r="D6" t="n">
-        <v>64.92592092495433</v>
+        <v>64.12088780747193</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>235.9532432386784</v>
+        <v>204.7523194500105</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>153.7956866087841</v>
+        <v>76.43887625265664</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.176534660315179</v>
+        <v>0.2964878066825367</v>
       </c>
       <c r="C2" t="n">
-        <v>2.54861704022472</v>
+        <v>2.950151851261665</v>
       </c>
       <c r="D2" t="n">
-        <v>11.71912234559418</v>
+        <v>8.711047379781949</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.19468914507713</v>
+        <v>1.124101121362598</v>
       </c>
       <c r="C3" t="n">
-        <v>20.88177366932966</v>
+        <v>9.100801218367932</v>
       </c>
       <c r="D3" t="n">
-        <v>71.17670855789376</v>
+        <v>38.58759351542088</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>5.066799901617788</v>
       </c>
       <c r="C4" t="n">
-        <v>75.27452347541994</v>
+        <v>52.23781359526853</v>
       </c>
       <c r="D4" t="n">
-        <v>147.1414006693992</v>
+        <v>100.557472102888</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.92878405260905</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C5" t="n">
-        <v>186.4584327290755</v>
+        <v>163.902779224005</v>
       </c>
       <c r="D5" t="n">
-        <v>138.2055330653448</v>
+        <v>116.2880155680347</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.34853010167018</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>284.7402136535194</v>
+        <v>322.3352602399468</v>
       </c>
       <c r="D6" t="n">
-        <v>77.08192099893833</v>
+        <v>80.46306009236434</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>287.8150474632204</v>
+        <v>328.2385091855828</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>42.81892612072463</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>197.1889351364931</v>
+        <v>173.3226484462531</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>77.54530591534278</v>
+        <v>61.12655730951914</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.856304982281471</v>
+        <v>0.2454369260617026</v>
       </c>
       <c r="C2" t="n">
-        <v>12.75486617357456</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="D2" t="n">
-        <v>15.73741569907637</v>
+        <v>9.398270772754715</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.41143440353742</v>
+        <v>1.055378782065321</v>
       </c>
       <c r="C3" t="n">
-        <v>15.81104677689488</v>
+        <v>10.32798584867645</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10950774564847</v>
+        <v>36.6437330610122</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.21761349964007</v>
+        <v>3.611849803924016</v>
       </c>
       <c r="C4" t="n">
-        <v>64.83461838845936</v>
+        <v>36.88426124855267</v>
       </c>
       <c r="D4" t="n">
-        <v>148.1241301213502</v>
+        <v>97.45613110517236</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.60971604872884</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="C5" t="n">
-        <v>165.7435561694678</v>
+        <v>130.0324834274901</v>
       </c>
       <c r="D5" t="n">
-        <v>153.4471661737765</v>
+        <v>125.3200944471054</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>290.4156971317702</v>
+        <v>294.4408627191822</v>
       </c>
       <c r="D6" t="n">
-        <v>94.75239792767668</v>
+        <v>95.51717938928493</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.54217107911827</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>338.2395730487451</v>
+        <v>396.2696980990698</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>54.43692845278139</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>270.9574576335984</v>
+        <v>293.9892587752286</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>137.8953007908027</v>
+        <v>132.3484262618082</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>24.07343545583603</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>52.52841091572559</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.373105185342792</v>
+        <v>1.647372647726148</v>
       </c>
       <c r="C2" t="n">
-        <v>8.078801858247003</v>
+        <v>17.89627890071511</v>
       </c>
       <c r="D2" t="n">
-        <v>6.665085164131596</v>
+        <v>13.48430471782994</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.755765805820797</v>
+        <v>0.1835868206941536</v>
       </c>
       <c r="C2" t="n">
-        <v>7.347399818583129</v>
+        <v>19.48081969536946</v>
       </c>
       <c r="D2" t="n">
-        <v>11.58265941470387</v>
+        <v>11.65629049252238</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.45132620651305</v>
+        <v>0.9277515805132359</v>
       </c>
       <c r="C3" t="n">
-        <v>27.94544840138546</v>
+        <v>24.86276061005047</v>
       </c>
       <c r="D3" t="n">
-        <v>71.36814936022188</v>
+        <v>35.56381058634071</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.93829843001524</v>
+        <v>2.846086594611503</v>
       </c>
       <c r="C4" t="n">
-        <v>93.48692513690251</v>
+        <v>31.58773238414112</v>
       </c>
       <c r="D4" t="n">
-        <v>151.3913864810837</v>
+        <v>94.15058658497337</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.53297549688156</v>
+        <v>7.657632093125122</v>
       </c>
       <c r="C5" t="n">
-        <v>245.4369260617026</v>
+        <v>100.5309649148734</v>
       </c>
       <c r="D5" t="n">
-        <v>138.7700379952867</v>
+        <v>129.2470852640926</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.95852991671016</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>279.7087566692545</v>
+        <v>257.4093393149925</v>
       </c>
       <c r="D6" t="n">
-        <v>76.11588125795947</v>
+        <v>110.0882788157161</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>190.5591928897144</v>
+        <v>409.3848656801029</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>65.33629146532947</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>397.5489153577034</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>231.0827928779099</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>90.96383353698822</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.275331325545611</v>
+        <v>3.594178345247573</v>
       </c>
       <c r="C2" t="n">
-        <v>4.984333094461056</v>
+        <v>9.479755832207202</v>
       </c>
       <c r="D2" t="n">
-        <v>14.84108004509903</v>
+        <v>15.92002077206628</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.41772580039041</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35653864755761</v>
+        <v>35.33309987584271</v>
       </c>
       <c r="D3" t="n">
-        <v>8.732645829275379</v>
+        <v>12.20803270230909</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39854868766088</v>
+        <v>11.67699143792841</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14534312951872</v>
+        <v>59.94188938136584</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576299845607162</v>
+        <v>0.778466095861894</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.513094196422587</v>
+        <v>2.000801821255</v>
       </c>
       <c r="C2" t="n">
-        <v>7.730281423239385</v>
+        <v>8.273187903687871</v>
       </c>
       <c r="D2" t="n">
-        <v>27.98766355266807</v>
+        <v>19.73411060306514</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.56346642897544</v>
+        <v>8.811185645615124</v>
       </c>
       <c r="C3" t="n">
-        <v>19.78221624057323</v>
+        <v>36.85480881742526</v>
       </c>
       <c r="D3" t="n">
-        <v>19.08517537055799</v>
+        <v>23.14961086613979</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.32427984203771</v>
+        <v>3.57356164345839</v>
       </c>
       <c r="C4" t="n">
-        <v>31.5494442236755</v>
+        <v>57.06212181393736</v>
       </c>
       <c r="D4" t="n">
-        <v>19.64182631886593</v>
+        <v>20.68836937159303</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44215663078099</v>
+        <v>13.62559512802456</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15097909804129</v>
+        <v>73.73851481048587</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250980343322313</v>
+        <v>1.603011191532302</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.040292713603124</v>
+        <v>1.340085616296896</v>
       </c>
       <c r="C2" t="n">
-        <v>6.935065782799468</v>
+        <v>4.489532251520663</v>
       </c>
       <c r="D2" t="n">
-        <v>20.80028860987717</v>
+        <v>23.53936470472577</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>7.755806863549802</v>
       </c>
       <c r="C3" t="n">
-        <v>26.02613163958294</v>
+        <v>33.95865308989718</v>
       </c>
       <c r="D3" t="n">
-        <v>37.04624961975339</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.07874510498477</v>
+        <v>11.47368541953247</v>
       </c>
       <c r="C4" t="n">
-        <v>42.15526467265379</v>
+        <v>78.93742415996479</v>
       </c>
       <c r="D4" t="n">
-        <v>24.79796526157018</v>
+        <v>28.01417074068274</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.78097245096173</v>
+        <v>4.098796665230434</v>
       </c>
       <c r="C5" t="n">
-        <v>35.51472320112837</v>
+        <v>65.26167863980673</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>27.39076094848602</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73453178459485</v>
+        <v>14.83083245505912</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0806438860286</v>
+        <v>87.33712445757038</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183632946148713</v>
+        <v>2.47180540917652</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324017800130453</v>
+        <v>0.97880246113407</v>
       </c>
       <c r="C2" t="n">
-        <v>6.252751128347935</v>
+        <v>10.18366893615216</v>
       </c>
       <c r="D2" t="n">
-        <v>19.91082518982956</v>
+        <v>26.63285172080747</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91060420565131</v>
+        <v>5.993569734426778</v>
       </c>
       <c r="C3" t="n">
-        <v>26.52682296874882</v>
+        <v>24.10681487778043</v>
       </c>
       <c r="D3" t="n">
-        <v>44.61061568097507</v>
+        <v>45.04258467084367</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.89479843139213</v>
+        <v>13.59229696529709</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98179842863836</v>
+        <v>82.49822308326797</v>
       </c>
       <c r="D4" t="n">
-        <v>37.088464771036</v>
+        <v>38.81143199198916</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.56823629877644</v>
+        <v>10.8973995171396</v>
       </c>
       <c r="C5" t="n">
-        <v>58.04583301359268</v>
+        <v>109.7839370273996</v>
       </c>
       <c r="D5" t="n">
-        <v>31.44047022850411</v>
+        <v>31.3668391506856</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>5.111960296013143</v>
       </c>
       <c r="C6" t="n">
-        <v>35.50196048097316</v>
+        <v>61.38377520803183</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05960393198509</v>
+        <v>16.06428874465712</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8174161277122</v>
+        <v>100.6131768744314</v>
       </c>
       <c r="D21" t="n">
-        <v>6.019867977328363</v>
+        <v>3.381955525190972</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.396667130244716</v>
+        <v>1.148644813968768</v>
       </c>
       <c r="C2" t="n">
-        <v>7.220754364735291</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="D2" t="n">
-        <v>22.81778014210436</v>
+        <v>21.30294343445154</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7128720064702</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C3" t="n">
-        <v>23.7141157960817</v>
+        <v>32.81491701444963</v>
       </c>
       <c r="D3" t="n">
-        <v>46.87354413926396</v>
+        <v>55.26257827205296</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.46238747316702</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="C4" t="n">
-        <v>51.34442318440394</v>
+        <v>70.30982533504381</v>
       </c>
       <c r="D4" t="n">
-        <v>43.94204549438299</v>
+        <v>51.90598287123311</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.98485717827558</v>
+        <v>15.53615741970578</v>
       </c>
       <c r="C5" t="n">
-        <v>60.05841580729864</v>
+        <v>132.3395905324701</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>37.87091769132071</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.03524510636165</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>44.19631814978292</v>
+        <v>118.8228881404</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>35.54221213684728</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29589127407256</v>
+        <v>52.81998998388688</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058201783285456</v>
+        <v>17.3189196285564</v>
       </c>
       <c r="C21" t="n">
-        <v>66.17064171830116</v>
+        <v>114.3048695484723</v>
       </c>
       <c r="D21" t="n">
-        <v>4.41137611455341</v>
+        <v>4.329729907139101</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.837070938824034</v>
+        <v>1.464767574736241</v>
       </c>
       <c r="C2" t="n">
-        <v>9.8341667534403</v>
+        <v>15.45859935107027</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87450052477243</v>
+        <v>20.09244851511522</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7303635386974</v>
+        <v>4.187153958612646</v>
       </c>
       <c r="C3" t="n">
-        <v>26.61518026213103</v>
+        <v>37.51257977927062</v>
       </c>
       <c r="D3" t="n">
-        <v>54.71279955767474</v>
+        <v>58.51707191163113</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.82272993835461</v>
+        <v>10.65687132959913</v>
       </c>
       <c r="C4" t="n">
-        <v>56.01557876121026</v>
+        <v>76.19343932659496</v>
       </c>
       <c r="D4" t="n">
-        <v>57.89169862402591</v>
+        <v>64.79633022799374</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.44613973055134</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>81.82867114897165</v>
+        <v>129.6643280383975</v>
       </c>
       <c r="D5" t="n">
-        <v>40.07985002587604</v>
+        <v>46.82936549257286</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.65539086027615</v>
+        <v>15.05411929692059</v>
       </c>
       <c r="C6" t="n">
-        <v>74.90833158173589</v>
+        <v>162.8581996666864</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>47.37030847761284</v>
+        <v>108.1552175860541</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>26.20284622634736</v>
+        <v>46.48084505756524</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280939647372778</v>
+        <v>17.70375736976008</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53974884149258</v>
+        <v>126.5818651937846</v>
       </c>
       <c r="D21" t="n">
-        <v>5.460704735529584</v>
+        <v>5.311127210928023</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.535273482992764</v>
+        <v>1.321432409916207</v>
       </c>
       <c r="C2" t="n">
-        <v>5.891467973185108</v>
+        <v>9.76937140496001</v>
       </c>
       <c r="D2" t="n">
-        <v>19.12444527872787</v>
+        <v>15.97696213891259</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18058482431918</v>
+        <v>6.307728999785756</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68376373270807</v>
+        <v>59.40555358397449</v>
       </c>
       <c r="D3" t="n">
-        <v>57.91820581204058</v>
+        <v>63.8332357301276</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>8.19366633964388</v>
       </c>
       <c r="C4" t="n">
-        <v>62.30759979772807</v>
+        <v>110.8059363875205</v>
       </c>
       <c r="D4" t="n">
-        <v>72.32633511956676</v>
+        <v>59.89544568839366</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>8.467573949128742</v>
       </c>
       <c r="C5" t="n">
-        <v>93.48692513690253</v>
+        <v>97.31574118346511</v>
       </c>
       <c r="D5" t="n">
-        <v>51.46812339513905</v>
+        <v>36.64373306101221</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>105.9021066048077</v>
+        <v>71.20517924131691</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>81.20624310447916</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>46.39739650270425</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491242087579725</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.21287874621937</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.554836826632259</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
